--- a/data/trans_orig/P1805_2016_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1805_2016_2023-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3845</t>
+          <t>3989</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15212</t>
+          <t>17122</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3704</t>
+          <t>3614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16931</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8797</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25666</t>
+          <t>26501</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404251</t>
+          <t>402341</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415618</t>
+          <t>415474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>378824</t>
+          <t>378081</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>392051</t>
+          <t>392141</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>789552</t>
+          <t>788717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>806421</t>
+          <t>805886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17006</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6428</t>
+          <t>6485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20201</t>
+          <t>20533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12327</t>
+          <t>12531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29977</t>
+          <t>30533</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>573490</t>
+          <t>575490</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>587463</t>
+          <t>587355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>543343</t>
+          <t>543011</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>557116</t>
+          <t>557059</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1124063</t>
+          <t>1123507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1141713</t>
+          <t>1141509</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10894</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27670</t>
+          <t>27390</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13808</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31051</t>
+          <t>31887</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>27528</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52611</t>
+          <t>51554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>641427</t>
+          <t>641707</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658748</t>
+          <t>658203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>630335</t>
+          <t>629499</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>647578</t>
+          <t>648077</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1277872</t>
+          <t>1278929</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1302581</t>
+          <t>1302955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6284</t>
+          <t>6324</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20993</t>
+          <t>20989</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18418</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41036</t>
+          <t>40812</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27619</t>
+          <t>27419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52931</t>
+          <t>53059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>625055</t>
+          <t>625059</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639764</t>
+          <t>639724</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>608041</t>
+          <t>608265</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>630855</t>
+          <t>630659</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1242194</t>
+          <t>1242066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1267506</t>
+          <t>1267706</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3352</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18301</t>
+          <t>17646</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38697</t>
+          <t>38867</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24839</t>
+          <t>24326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49377</t>
+          <t>49560</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460811</t>
+          <t>462658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>474566</t>
+          <t>474781</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>458152</t>
+          <t>457982</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>478548</t>
+          <t>479203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>925390</t>
+          <t>925207</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>949928</t>
+          <t>950441</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8495</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9104</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26760</t>
+          <t>27423</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>12336</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>32657</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>325835</t>
+          <t>324868</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>333367</t>
+          <t>333405</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,12 +2574,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>351002</t>
+          <t>350339</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>368658</t>
+          <t>368695</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>680205</t>
+          <t>679435</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>699426</t>
+          <t>699756</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1247</t>
+          <t>896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10283</t>
+          <t>10247</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30567</t>
+          <t>32357</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>13538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>34738</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247547</t>
+          <t>247933</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255751</t>
+          <t>256102</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>369602</t>
+          <t>367812</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>389886</t>
+          <t>389922</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>622967</t>
+          <t>622429</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>644620</t>
+          <t>643629</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47645</t>
+          <t>47184</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77454</t>
+          <t>78455</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>110010</t>
+          <t>108863</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>160910</t>
+          <t>155830</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167506</t>
+          <t>164728</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>223618</t>
+          <t>223541</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,7 +3217,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3316896</t>
+          <t>3315895</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3346705</t>
+          <t>3347166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3383632</t>
+          <t>3388712</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3434532</t>
+          <t>3435679</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6715274</t>
+          <t>6715351</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6771386</t>
+          <t>6774164</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37660</t>
+          <t>37021</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18077</t>
+          <t>20055</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8958</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33630</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>36031</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21654</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60746</t>
+          <t>57543</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>382032</t>
+          <t>389379</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362327</t>
+          <t>370772</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>393455</t>
+          <t>400277</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>295123</t>
+          <t>342457</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279570</t>
+          <t>327667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>304242</t>
+          <t>352541</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>90,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>677156</t>
+          <t>731835</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>652441</t>
+          <t>712762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>691533</t>
+          <t>748697</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5036</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22009</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>19727</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31391</t>
+          <t>31654</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>29134</t>
+          <t>32623</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>21199</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44594</t>
+          <t>49955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>412744</t>
+          <t>463995</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>401538</t>
+          <t>451326</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418511</t>
+          <t>470697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>493172</t>
+          <t>481356</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>480113</t>
+          <t>469429</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>501475</t>
+          <t>489469</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>905917</t>
+          <t>945350</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890457</t>
+          <t>928018</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>917254</t>
+          <t>956774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>23400</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37001</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,32 +4426,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24758</t>
+          <t>27315</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16685</t>
+          <t>19463</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>36356</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4461,32 +4461,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48158</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36518</t>
+          <t>38757</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62673</t>
+          <t>66612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>512938</t>
+          <t>596341</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>499337</t>
+          <t>581438</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>521773</t>
+          <t>605694</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,32 +4539,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>517710</t>
+          <t>594824</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>508775</t>
+          <t>585783</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>525783</t>
+          <t>602676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4574,32 +4574,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1030648</t>
+          <t>1191165</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1016133</t>
+          <t>1176364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1042288</t>
+          <t>1204219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>34528</t>
+          <t>36756</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>25359</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54372</t>
+          <t>53016</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30806</t>
+          <t>33574</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>24263</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>65335</t>
+          <t>70330</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>38788</t>
+          <t>56810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>86756</t>
+          <t>90224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>853258</t>
+          <t>663861</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833414</t>
+          <t>647601</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>873799</t>
+          <t>675258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>682075</t>
+          <t>703312</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>672175</t>
+          <t>693861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>689714</t>
+          <t>712623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1535332</t>
+          <t>1367174</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1513911</t>
+          <t>1347280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1561879</t>
+          <t>1380694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>96,05%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11122</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26158</t>
+          <t>27279</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>30705</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>23842</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>40107</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>46595</t>
+          <t>48445</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37206</t>
+          <t>37726</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59105</t>
+          <t>61376</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>543545</t>
+          <t>591606</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535076</t>
+          <t>582067</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>550112</t>
+          <t>598044</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>518321</t>
+          <t>577466</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>509647</t>
+          <t>568064</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>525898</t>
+          <t>584329</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1061865</t>
+          <t>1169072</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1049355</t>
+          <t>1156141</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1071254</t>
+          <t>1179791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547227</t>
+          <t>608171</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547227</t>
+          <t>608171</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547227</t>
+          <t>608171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1108460</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1108460</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1108460</t>
+          <t>1217517</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1220</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>7236</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>14270</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5113</t>
+          <t>9775</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24126</t>
+          <t>20633</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>17803</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>12030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25687</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>364669</t>
+          <t>403547</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>361139</t>
+          <t>399844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>366945</t>
+          <t>405714</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>595059</t>
+          <t>424896</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>584242</t>
+          <t>418533</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>603255</t>
+          <t>429391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>959728</t>
+          <t>828443</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>950942</t>
+          <t>820559</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>968409</t>
+          <t>834216</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3330</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10622</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>7097</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15945</t>
+          <t>18001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13675</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>9300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20093</t>
+          <t>22463</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>279706</t>
+          <t>306868</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>276113</t>
+          <t>302992</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>281651</t>
+          <t>309125</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>414643</t>
+          <t>452468</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>409320</t>
+          <t>446012</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>419008</t>
+          <t>456916</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>694349</t>
+          <t>759336</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>687931</t>
+          <t>751748</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>698942</t>
+          <t>764911</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>110924</t>
+          <t>117165</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>83475</t>
+          <t>92163</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>141676</t>
+          <t>144233</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>144810</t>
+          <t>157192</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114398</t>
+          <t>135152</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>170710</t>
+          <t>181297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>255734</t>
+          <t>274357</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>220482</t>
+          <t>240328</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>297091</t>
+          <t>309782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3348893</t>
+          <t>3415597</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3318141</t>
+          <t>3388529</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3376342</t>
+          <t>3440599</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3516103</t>
+          <t>3576778</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3490203</t>
+          <t>3552673</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3546515</t>
+          <t>3598818</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6864996</t>
+          <t>6992375</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6823639</t>
+          <t>6956950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6900248</t>
+          <t>7026404</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3660913</t>
+          <t>3733970</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7120730</t>
+          <t>7266732</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
